--- a/data/Verdbolguvaentingar-a-mismunandi-maelikvarda.xlsx
+++ b/data/Verdbolguvaentingar-a-mismunandi-maelikvarda.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29917"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{003F287D-E07A-4CC2-B155-C76AE3B3BB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8FAC441-14C5-4A11-BF39-513E7A1010AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/Verdbolguvaentingar-a-mismunandi-maelikvarda.xlsx
+++ b/data/Verdbolguvaentingar-a-mismunandi-maelikvarda.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30117"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30219"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18589B18-870A-41B4-95F7-81AB15EFD4C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E35808F1-2AB7-4241-A8DA-0A711C05C587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18885" yWindow="4425" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heimili_Households" sheetId="2" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="124">
   <si>
     <t>Verðbólguvæntingar heimila / Household inflation expectations</t>
   </si>
@@ -358,6 +358,9 @@
   </si>
   <si>
     <t>2026Q1</t>
+  </si>
+  <si>
+    <t>2026Q2</t>
   </si>
   <si>
     <t>Meðaltal / average</t>
@@ -983,7 +986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CP35"/>
+  <dimension ref="A1:CQ35"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="70.140625" style="2" customWidth="1"/>
@@ -996,11 +999,11 @@
     <col min="49" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:94" ht="17.25">
+    <row r="1" spans="1:95" ht="17.25">
       <c r="A1" s="8"/>
       <c r="CP1"/>
     </row>
-    <row r="2" spans="1:94">
+    <row r="2" spans="1:95">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
@@ -1050,33 +1053,33 @@
       <c r="AS2" s="10"/>
       <c r="CP2"/>
     </row>
-    <row r="3" spans="1:94" ht="17.25">
+    <row r="3" spans="1:95" ht="17.25">
       <c r="A3" s="8"/>
       <c r="CP3"/>
     </row>
-    <row r="4" spans="1:94">
+    <row r="4" spans="1:95">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="CP4"/>
     </row>
-    <row r="5" spans="1:94">
+    <row r="5" spans="1:95">
       <c r="A5" s="11"/>
       <c r="CP5"/>
     </row>
-    <row r="6" spans="1:94">
+    <row r="6" spans="1:95">
       <c r="A6" s="12" t="s">
         <v>2</v>
       </c>
       <c r="CP6"/>
     </row>
-    <row r="7" spans="1:94">
+    <row r="7" spans="1:95">
       <c r="A7" s="13" t="s">
         <v>3</v>
       </c>
       <c r="CP7"/>
     </row>
-    <row r="8" spans="1:94">
+    <row r="8" spans="1:95">
       <c r="A8" s="14" t="s">
         <v>4</v>
       </c>
@@ -1163,8 +1166,9 @@
       <c r="CN8" s="15"/>
       <c r="CO8" s="15"/>
       <c r="CP8" s="15"/>
+      <c r="CQ8" s="15"/>
     </row>
-    <row r="9" spans="1:94">
+    <row r="9" spans="1:95">
       <c r="B9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1217,7 +1221,7 @@
       <c r="CA9" s="16"/>
       <c r="CP9"/>
     </row>
-    <row r="10" spans="1:94">
+    <row r="10" spans="1:95">
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1497,10 +1501,13 @@
       <c r="CP10" s="4" t="s">
         <v>98</v>
       </c>
+      <c r="CQ10" s="4" t="s">
+        <v>99</v>
+      </c>
     </row>
-    <row r="11" spans="1:94">
+    <row r="11" spans="1:95">
       <c r="A11" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B11" s="5">
         <v>3.6</v>
@@ -1781,10 +1788,13 @@
       <c r="CP11" s="2">
         <v>5.8</v>
       </c>
+      <c r="CQ11" s="2">
+        <v>6.3</v>
+      </c>
     </row>
-    <row r="12" spans="1:94">
+    <row r="12" spans="1:95">
       <c r="A12" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B12" s="5">
         <v>3</v>
@@ -2065,10 +2075,13 @@
       <c r="CP12" s="2">
         <v>5</v>
       </c>
+      <c r="CQ12" s="2">
+        <v>5.3</v>
+      </c>
     </row>
-    <row r="13" spans="1:94">
+    <row r="13" spans="1:95">
       <c r="A13" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B13" s="5">
         <v>2.5</v>
@@ -2349,8 +2362,11 @@
       <c r="CP13" s="2">
         <v>2.7</v>
       </c>
+      <c r="CQ13" s="2">
+        <v>2.8</v>
+      </c>
     </row>
-    <row r="14" spans="1:94">
+    <row r="14" spans="1:95">
       <c r="A14" s="15"/>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
@@ -2439,8 +2455,9 @@
       <c r="CN14" s="15"/>
       <c r="CO14" s="15"/>
       <c r="CP14" s="15"/>
+      <c r="CQ14" s="15"/>
     </row>
-    <row r="15" spans="1:94">
+    <row r="15" spans="1:95">
       <c r="BV15" s="16"/>
       <c r="BW15" s="16"/>
       <c r="BX15" s="16"/>
@@ -2449,21 +2466,21 @@
       <c r="CA15" s="16"/>
       <c r="CP15"/>
     </row>
-    <row r="16" spans="1:94">
+    <row r="16" spans="1:95">
       <c r="A16" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="CP16"/>
     </row>
-    <row r="17" spans="1:94">
+    <row r="17" spans="1:95">
       <c r="A17" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="CP17"/>
     </row>
-    <row r="18" spans="1:94">
+    <row r="18" spans="1:95">
       <c r="A18" s="14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
@@ -2547,8 +2564,9 @@
       <c r="CN18" s="15"/>
       <c r="CO18" s="15"/>
       <c r="CP18" s="15"/>
+      <c r="CQ18" s="15"/>
     </row>
-    <row r="19" spans="1:94">
+    <row r="19" spans="1:95">
       <c r="B19" s="3" t="s">
         <v>5</v>
       </c>
@@ -2602,7 +2620,7 @@
       <c r="CB19" s="16"/>
       <c r="CP19"/>
     </row>
-    <row r="20" spans="1:94">
+    <row r="20" spans="1:95">
       <c r="B20" s="1" t="s">
         <v>6</v>
       </c>
@@ -2882,10 +2900,13 @@
       <c r="CP20" s="4" t="s">
         <v>98</v>
       </c>
+      <c r="CQ20" s="4" t="s">
+        <v>99</v>
+      </c>
     </row>
-    <row r="21" spans="1:94">
+    <row r="21" spans="1:95">
       <c r="A21" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -3120,10 +3141,13 @@
       <c r="CP21" s="2">
         <v>5.5</v>
       </c>
+      <c r="CQ21" s="2">
+        <v>5.8</v>
+      </c>
     </row>
-    <row r="22" spans="1:94">
+    <row r="22" spans="1:95">
       <c r="A22" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -3358,10 +3382,13 @@
       <c r="CP22" s="2">
         <v>4.7</v>
       </c>
+      <c r="CQ22" s="2">
+        <v>5</v>
+      </c>
     </row>
-    <row r="23" spans="1:94">
+    <row r="23" spans="1:95">
       <c r="A23" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
@@ -3596,8 +3623,11 @@
       <c r="CP23" s="2">
         <v>3.1</v>
       </c>
+      <c r="CQ23" s="2">
+        <v>3.4</v>
+      </c>
     </row>
-    <row r="24" spans="1:94">
+    <row r="24" spans="1:95">
       <c r="A24" s="15"/>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -3685,8 +3715,9 @@
       <c r="CN24" s="15"/>
       <c r="CO24" s="15"/>
       <c r="CP24" s="15"/>
+      <c r="CQ24" s="15"/>
     </row>
-    <row r="25" spans="1:94">
+    <row r="25" spans="1:95">
       <c r="BV25" s="16"/>
       <c r="BW25" s="16"/>
       <c r="BX25" s="16"/>
@@ -3696,21 +3727,21 @@
       <c r="CB25" s="16"/>
       <c r="CP25"/>
     </row>
-    <row r="26" spans="1:94">
+    <row r="26" spans="1:95">
       <c r="A26" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="CP26"/>
     </row>
-    <row r="27" spans="1:94">
+    <row r="27" spans="1:95">
       <c r="A27" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="CP27"/>
     </row>
-    <row r="28" spans="1:94">
+    <row r="28" spans="1:95">
       <c r="A28" s="14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -3794,8 +3825,9 @@
       <c r="CN28" s="15"/>
       <c r="CO28" s="15"/>
       <c r="CP28" s="15"/>
+      <c r="CQ28" s="15"/>
     </row>
-    <row r="29" spans="1:94">
+    <row r="29" spans="1:95">
       <c r="B29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3849,7 +3881,7 @@
       <c r="CB29" s="16"/>
       <c r="CP29"/>
     </row>
-    <row r="30" spans="1:94">
+    <row r="30" spans="1:95">
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
@@ -4129,10 +4161,13 @@
       <c r="CP30" s="4" t="s">
         <v>98</v>
       </c>
+      <c r="CQ30" s="4" t="s">
+        <v>99</v>
+      </c>
     </row>
-    <row r="31" spans="1:94">
+    <row r="31" spans="1:95">
       <c r="A31" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
@@ -4293,10 +4328,13 @@
       <c r="CP31" s="2">
         <v>5.2</v>
       </c>
+      <c r="CQ31" s="2">
+        <v>5.4</v>
+      </c>
     </row>
-    <row r="32" spans="1:94">
+    <row r="32" spans="1:95">
       <c r="A32" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -4457,10 +4495,13 @@
       <c r="CP32" s="2">
         <v>4.3</v>
       </c>
+      <c r="CQ32" s="2">
+        <v>5</v>
+      </c>
     </row>
-    <row r="33" spans="1:94">
+    <row r="33" spans="1:95">
       <c r="A33" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
@@ -4621,8 +4662,11 @@
       <c r="CP33" s="2">
         <v>2.7</v>
       </c>
+      <c r="CQ33" s="2">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="1:94">
+    <row r="34" spans="1:95">
       <c r="A34" s="15"/>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -4710,10 +4754,11 @@
       <c r="CN34" s="15"/>
       <c r="CO34" s="15"/>
       <c r="CP34" s="15"/>
+      <c r="CQ34" s="15"/>
     </row>
-    <row r="35" spans="1:94">
+    <row r="35" spans="1:95">
       <c r="A35" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BV35" s="16"/>
       <c r="BW35" s="16"/>
@@ -4733,7 +4778,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:CP39"/>
+  <dimension ref="A1:CQ39"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="65.140625" style="2" customWidth="1"/>
@@ -4746,13 +4791,13 @@
     <col min="49" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:94" ht="17.25">
+    <row r="1" spans="1:95" ht="17.25">
       <c r="A1" s="8"/>
       <c r="CP1"/>
     </row>
-    <row r="2" spans="1:94">
+    <row r="2" spans="1:95">
       <c r="A2" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -4800,35 +4845,35 @@
       <c r="AS2" s="10"/>
       <c r="CP2"/>
     </row>
-    <row r="3" spans="1:94" ht="17.25">
+    <row r="3" spans="1:95" ht="17.25">
       <c r="A3" s="8"/>
       <c r="CP3"/>
     </row>
-    <row r="4" spans="1:94">
+    <row r="4" spans="1:95">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="CP4"/>
     </row>
-    <row r="5" spans="1:94">
+    <row r="5" spans="1:95">
       <c r="A5" s="11"/>
       <c r="CP5"/>
     </row>
-    <row r="6" spans="1:94">
+    <row r="6" spans="1:95">
       <c r="A6" s="12" t="s">
         <v>2</v>
       </c>
       <c r="CP6"/>
     </row>
-    <row r="7" spans="1:94">
+    <row r="7" spans="1:95">
       <c r="A7" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="CP7"/>
     </row>
-    <row r="8" spans="1:94">
+    <row r="8" spans="1:95">
       <c r="A8" s="14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
@@ -4913,8 +4958,9 @@
       <c r="CN8" s="15"/>
       <c r="CO8" s="15"/>
       <c r="CP8" s="15"/>
+      <c r="CQ8" s="15"/>
     </row>
-    <row r="9" spans="1:94">
+    <row r="9" spans="1:95">
       <c r="B9" s="3" t="s">
         <v>5</v>
       </c>
@@ -4967,7 +5013,7 @@
       <c r="CB9" s="16"/>
       <c r="CP9"/>
     </row>
-    <row r="10" spans="1:94">
+    <row r="10" spans="1:95">
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
@@ -5247,10 +5293,13 @@
       <c r="CP10" s="4" t="s">
         <v>98</v>
       </c>
+      <c r="CQ10" s="4" t="s">
+        <v>99</v>
+      </c>
     </row>
-    <row r="11" spans="1:94">
+    <row r="11" spans="1:95">
       <c r="A11" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B11" s="5">
         <v>2.1</v>
@@ -5517,10 +5566,13 @@
       <c r="CP11" s="2">
         <v>4.7</v>
       </c>
+      <c r="CQ11" s="2">
+        <v>4.8</v>
+      </c>
     </row>
-    <row r="12" spans="1:94">
+    <row r="12" spans="1:95">
       <c r="A12" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B12" s="5">
         <v>2</v>
@@ -5785,10 +5837,13 @@
       <c r="CP12" s="2">
         <v>4.5</v>
       </c>
+      <c r="CQ12" s="2">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:94">
+    <row r="13" spans="1:95">
       <c r="A13" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B13" s="5">
         <v>1.9</v>
@@ -6055,8 +6110,11 @@
       <c r="CP13" s="2">
         <v>1.3</v>
       </c>
+      <c r="CQ13" s="2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" spans="1:94">
+    <row r="14" spans="1:95">
       <c r="A14" s="15"/>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
@@ -6144,8 +6202,9 @@
       <c r="CN14" s="15"/>
       <c r="CO14" s="15"/>
       <c r="CP14" s="15"/>
+      <c r="CQ14" s="15"/>
     </row>
-    <row r="15" spans="1:94">
+    <row r="15" spans="1:95">
       <c r="BV15" s="16"/>
       <c r="BW15" s="16"/>
       <c r="BX15" s="16"/>
@@ -6155,21 +6214,21 @@
       <c r="CB15" s="16"/>
       <c r="CP15"/>
     </row>
-    <row r="16" spans="1:94">
+    <row r="16" spans="1:95">
       <c r="A16" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="CP16"/>
     </row>
-    <row r="17" spans="1:94">
+    <row r="17" spans="1:95">
       <c r="A17" s="13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="CP17"/>
     </row>
-    <row r="18" spans="1:94">
+    <row r="18" spans="1:95">
       <c r="A18" s="14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
@@ -6255,8 +6314,9 @@
       <c r="CN18" s="15"/>
       <c r="CO18" s="15"/>
       <c r="CP18" s="15"/>
+      <c r="CQ18" s="15"/>
     </row>
-    <row r="19" spans="1:94">
+    <row r="19" spans="1:95">
       <c r="B19" s="3" t="s">
         <v>5</v>
       </c>
@@ -6308,7 +6368,7 @@
       <c r="CB19" s="16"/>
       <c r="CP19"/>
     </row>
-    <row r="20" spans="1:94">
+    <row r="20" spans="1:95">
       <c r="B20" s="1" t="s">
         <v>6</v>
       </c>
@@ -6588,10 +6648,13 @@
       <c r="CP20" s="4" t="s">
         <v>98</v>
       </c>
+      <c r="CQ20" s="4" t="s">
+        <v>99</v>
+      </c>
     </row>
-    <row r="21" spans="1:94">
+    <row r="21" spans="1:95">
       <c r="A21" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -6794,10 +6857,13 @@
       <c r="CP21" s="2">
         <v>4.0999999999999996</v>
       </c>
+      <c r="CQ21" s="2">
+        <v>4.3</v>
+      </c>
     </row>
-    <row r="22" spans="1:94">
+    <row r="22" spans="1:95">
       <c r="A22" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -7000,10 +7066,13 @@
       <c r="CP22" s="2">
         <v>4</v>
       </c>
+      <c r="CQ22" s="2">
+        <v>4</v>
+      </c>
     </row>
-    <row r="23" spans="1:94">
+    <row r="23" spans="1:95">
       <c r="A23" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
@@ -7206,8 +7275,11 @@
       <c r="CP23" s="2">
         <v>1.1000000000000001</v>
       </c>
+      <c r="CQ23" s="2">
+        <v>1.1000000000000001</v>
+      </c>
     </row>
-    <row r="24" spans="1:94">
+    <row r="24" spans="1:95">
       <c r="A24" s="15"/>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -7295,8 +7367,9 @@
       <c r="CN24" s="15"/>
       <c r="CO24" s="15"/>
       <c r="CP24" s="15"/>
+      <c r="CQ24" s="15"/>
     </row>
-    <row r="25" spans="1:94">
+    <row r="25" spans="1:95">
       <c r="BV25" s="16"/>
       <c r="BW25" s="16"/>
       <c r="BX25" s="16"/>
@@ -7306,21 +7379,21 @@
       <c r="CB25" s="16"/>
       <c r="CP25"/>
     </row>
-    <row r="26" spans="1:94">
+    <row r="26" spans="1:95">
       <c r="A26" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="CP26"/>
     </row>
-    <row r="27" spans="1:94">
+    <row r="27" spans="1:95">
       <c r="A27" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="CP27"/>
     </row>
-    <row r="28" spans="1:94">
+    <row r="28" spans="1:95">
       <c r="A28" s="14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -7406,8 +7479,9 @@
       <c r="CN28" s="15"/>
       <c r="CO28" s="15"/>
       <c r="CP28" s="15"/>
+      <c r="CQ28" s="15"/>
     </row>
-    <row r="29" spans="1:94">
+    <row r="29" spans="1:95">
       <c r="B29" s="3" t="s">
         <v>5</v>
       </c>
@@ -7459,7 +7533,7 @@
       <c r="CB29" s="16"/>
       <c r="CP29"/>
     </row>
-    <row r="30" spans="1:94">
+    <row r="30" spans="1:95">
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
@@ -7739,10 +7813,13 @@
       <c r="CP30" s="4" t="s">
         <v>98</v>
       </c>
+      <c r="CQ30" s="4" t="s">
+        <v>99</v>
+      </c>
     </row>
-    <row r="31" spans="1:94">
+    <row r="31" spans="1:95">
       <c r="A31" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
@@ -7901,10 +7978,13 @@
       <c r="CP31" s="2">
         <v>4</v>
       </c>
+      <c r="CQ31" s="2">
+        <v>4.0999999999999996</v>
+      </c>
     </row>
-    <row r="32" spans="1:94">
+    <row r="32" spans="1:95">
       <c r="A32" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -8063,10 +8143,13 @@
       <c r="CP32" s="2">
         <v>4</v>
       </c>
+      <c r="CQ32" s="2">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="1:94">
+    <row r="33" spans="1:95">
       <c r="A33" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
@@ -8225,8 +8308,11 @@
       <c r="CP33" s="2">
         <v>1.1000000000000001</v>
       </c>
+      <c r="CQ33" s="2">
+        <v>1.1000000000000001</v>
+      </c>
     </row>
-    <row r="34" spans="1:94">
+    <row r="34" spans="1:95">
       <c r="A34" s="15"/>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -8314,8 +8400,9 @@
       <c r="CN34" s="15"/>
       <c r="CO34" s="15"/>
       <c r="CP34" s="15"/>
+      <c r="CQ34" s="15"/>
     </row>
-    <row r="35" spans="1:94">
+    <row r="35" spans="1:95">
       <c r="BV35" s="16"/>
       <c r="BW35" s="16"/>
       <c r="BX35" s="16"/>
@@ -8325,21 +8412,21 @@
       <c r="CB35" s="16"/>
       <c r="CP35"/>
     </row>
-    <row r="36" spans="1:94">
+    <row r="36" spans="1:95">
       <c r="A36" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="CP36"/>
     </row>
-    <row r="37" spans="1:94">
+    <row r="37" spans="1:95">
       <c r="A37" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="CP37"/>
     </row>
-    <row r="39" spans="1:94">
+    <row r="39" spans="1:95">
       <c r="A39" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="CP39"/>
     </row>
@@ -8363,7 +8450,7 @@
   <sheetData>
     <row r="2" spans="1:94" ht="17.25">
       <c r="A2" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:94">
@@ -8691,7 +8778,7 @@
     </row>
     <row r="6" spans="1:94">
       <c r="A6" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B6" s="5">
         <v>1.6728464306933859</v>
@@ -8975,7 +9062,7 @@
     </row>
     <row r="7" spans="1:94">
       <c r="A7" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B7" s="5">
         <v>1.8918263341286843</v>
@@ -9259,7 +9346,7 @@
     </row>
     <row r="8" spans="1:94">
       <c r="A8" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B8" s="5">
         <v>2.4902406917840634</v>
@@ -9543,7 +9630,7 @@
     </row>
     <row r="9" spans="1:94">
       <c r="A9" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B9" s="5">
         <v>2.9083419565991613</v>
@@ -9830,12 +9917,12 @@
     </row>
     <row r="12" spans="1:94" ht="49.5">
       <c r="A12" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:94" ht="49.5">
       <c r="A13" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:94">
@@ -9843,7 +9930,7 @@
     </row>
     <row r="15" spans="1:94">
       <c r="A15" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:94">
